--- a/artfynd/A 6778-2022 artfynd.xlsx
+++ b/artfynd/A 6778-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6778-2022 artfynd.xlsx
+++ b/artfynd/A 6778-2022 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114752516</v>
+        <v>114752505</v>
       </c>
       <c r="B2" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>102613</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sickusen, Dlr</t>
@@ -766,6 +766,11 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hörs i väster från obspunkten</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,50 +797,40 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114752505</v>
+        <v>114752516</v>
       </c>
       <c r="B3" t="n">
-        <v>56481</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sickusen, Dlr</t>
@@ -888,11 +883,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hörs i väster från obspunkten</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 6778-2022 artfynd.xlsx
+++ b/artfynd/A 6778-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114752505</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,8 +916,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114752516</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>